--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_13-01-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_13-01-2026.xlsx
@@ -1918,7 +1918,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£690.00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>£2157.92</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
